--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1550</v>
+        <v>2076</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1169</v>
+        <v>1552</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>710</v>
+        <v>973</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>196</v>
+        <v>289</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>235</v>
+        <v>367</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>301</v>
+        <v>401</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>183</v>
+        <v>246</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>209</v>
+        <v>275</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>243</v>
+        <v>372</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>144</v>
+        <v>199</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>198</v>
+        <v>272</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>151</v>
+        <v>199</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>162</v>
+        <v>222</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>230</v>
+        <v>328</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,35 +1091,35 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>13</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>151</v>
+        <v>218</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>5</v>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01043</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,51 +1195,51 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1253,47 +1253,47 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="F19" s="12" t="n">
-        <v>97</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="J19" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="K19" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K19" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="L19" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01043</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H21" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="K21" s="12" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I22" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="M22" s="12" t="n">
         <v>23</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1469,47 +1469,47 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VENTIMIGLIA</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1577,31 +1577,31 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F25" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="G25" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>50</v>
-      </c>
       <c r="H25" s="12" t="n">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>VENTIMIGLIA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F26" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="J26" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K26" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="M26" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L26" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1739,47 +1739,47 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I28" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="J28" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="M29" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1901,47 +1901,47 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1955,28 +1955,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>12</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>01086</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>RECCO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,35 +2005,35 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H33" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="G33" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H33" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="I33" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>1</v>
@@ -2084,10 +2084,10 @@
         <v>0</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01086</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>RECCO</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,35 +2113,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01288</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>BOLANO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,35 +2167,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>19</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,12 +2206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>01288</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>BOLANO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,39 +2221,39 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>0</v>
@@ -2300,14 +2300,14 @@
         <v>0</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2336,13 +2336,13 @@
         <v>0</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>0</v>
@@ -2390,13 +2390,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>401</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.04738154613466334</v>
+        <v>19</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>227</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.03083700440528634</v>
+        <v>7</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>170</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.2529411764705882</v>
+        <v>43</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1615384615384615</v>
+        <v>21</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>328</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.02134146341463415</v>
+        <v>7</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>128</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.0625</v>
+        <v>8</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>114</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.04385964912280702</v>
+        <v>5</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>117</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.1282051282051282</v>
+        <v>15</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>71</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.04225352112676056</v>
+        <v>3</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>157</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.286624203821656</v>
+        <v>45</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>62</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.01612903225806452</v>
+        <v>1</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>90</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.2555555555555555</v>
+        <v>23</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>66</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.7424242424242424</v>
+        <v>49</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>69</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.1449275362318841</v>
+        <v>10</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>52</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.07692307692307693</v>
+        <v>4</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>36</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.25</v>
+        <v>9</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>65</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.1384615384615385</v>
+        <v>9</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>48</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.7708333333333334</v>
+        <v>37</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>64</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.265625</v>
+        <v>17</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>65</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.04615384615384616</v>
+        <v>3</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>55</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.2363636363636364</v>
+        <v>13</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>98</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0.03061224489795918</v>
+        <v>3</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>48</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.04166666666666666</v>
+        <v>2</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>23</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.6956521739130435</v>
+        <v>16</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>33</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0.5757575757575758</v>
+        <v>19</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2076</v>
+        <v>2205</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1552</v>
+        <v>1649</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>973</v>
+        <v>1033</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>7</v>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>7</v>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>4</v>
@@ -1103,19 +1103,19 @@
         <v>9</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>46</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>5</v>
@@ -1199,47 +1199,47 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>15</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1469,47 +1469,47 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>27</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>49</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>01480</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1523,47 +1523,47 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01480</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1577,35 +1577,35 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1631,16 +1631,16 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>35</v>
@@ -1649,13 +1649,13 @@
         <v>8</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1688,32 +1688,32 @@
         <v>39</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>27</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>9</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>36</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>33</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>8</v>
@@ -1760,10 +1760,10 @@
         <v>9</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>7</v>
@@ -1814,10 +1814,10 @@
         <v>14</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>16</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>3</v>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1904,28 +1904,28 @@
         <v>31</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1955,31 +1955,31 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2012,13 +2012,13 @@
         <v>27</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>18</v>
@@ -2030,7 +2030,7 @@
         <v>9</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>3</v>
@@ -2063,35 +2063,35 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J34" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2117,19 +2117,19 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>7</v>
@@ -2138,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2171,19 +2171,19 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>2</v>
@@ -2192,7 +2192,7 @@
         <v>2</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>19</v>
@@ -2228,13 +2228,13 @@
         <v>13</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>16</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>14</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>0</v>
@@ -2300,14 +2300,14 @@
         <v>0</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2390,13 +2390,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2205</v>
+        <v>2333</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1649</v>
+        <v>1746</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1033</v>
+        <v>1100</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="J11" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="K11" s="12" t="n">
-        <v>72</v>
-      </c>
       <c r="L11" s="12" t="n">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>7</v>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>50</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>01351</t>
+          <t>01032</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,51 +979,51 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>114</v>
+        <v>238</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>138</v>
+        <v>377</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>01032</t>
+          <t>01351</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,39 +1033,39 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>118</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="L15" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="F15" s="12" t="n">
-        <v>228</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>107</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>345</v>
-      </c>
       <c r="M15" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1091,35 +1091,35 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>29</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>5</v>
@@ -1199,35 +1199,35 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>15</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>48</v>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>4</v>
@@ -1319,19 +1319,19 @@
         <v>2</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>5</v>
@@ -1373,19 +1373,19 @@
         <v>9</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>7</v>
@@ -1427,16 +1427,16 @@
         <v>15</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>35</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>1</v>
@@ -1469,31 +1469,31 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>4</v>
@@ -1577,31 +1577,31 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>17</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1634,13 +1634,13 @@
         <v>46</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>35</v>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K28" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>9</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="M28" s="12" t="n">
-        <v>40</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1793,31 +1793,31 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>24</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1955,31 +1955,31 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2009,28 +2009,28 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>62</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>3</v>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,51 +2059,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I34" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J34" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>52</v>
-      </c>
       <c r="M34" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,39 +2113,39 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
@@ -2189,13 +2189,13 @@
         <v>2</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>16</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>14</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>0</v>
@@ -2390,13 +2390,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2333</v>
+        <v>2459</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1746</v>
+        <v>1842</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1100</v>
+        <v>1145</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="G11" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="H11" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>241</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>75</v>
-      </c>
       <c r="L11" s="12" t="n">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>46</v>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>01032</t>
+          <t>01351</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,51 +979,51 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>238</v>
+        <v>139</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>377</v>
+        <v>159</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>01351</t>
+          <t>01032</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,39 +1033,39 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>128</v>
+        <v>242</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>148</v>
+        <v>403</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>5</v>
@@ -1103,16 +1103,16 @@
         <v>9</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>51</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>10</v>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>5</v>
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>26</v>
@@ -1220,14 +1220,14 @@
         <v>24</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>8</v>
@@ -1274,26 +1274,26 @@
         <v>44</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1307,47 +1307,47 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1361,47 +1361,47 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1469,47 +1469,47 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01480</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1523,47 +1523,47 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K24" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="M24" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L24" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>01480</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1577,35 +1577,35 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G28" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>12</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,39 +1789,39 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>21</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>15</v>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>2</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -2009,19 +2009,19 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>25</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>6</v>
@@ -2030,7 +2030,7 @@
         <v>11</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>3</v>
@@ -2063,22 +2063,22 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="G34" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F34" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="G34" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="H34" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>0</v>
@@ -2120,13 +2120,13 @@
         <v>23</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>12</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>25</v>
@@ -2138,14 +2138,14 @@
         <v>1</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2171,19 +2171,19 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>2</v>
@@ -2192,7 +2192,7 @@
         <v>3</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>20</v>
@@ -2225,19 +2225,19 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>3</v>
@@ -2279,22 +2279,22 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>0</v>
@@ -2390,13 +2390,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N40" headerRowCount="1">
-  <autoFilter ref="A10:N40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N41" headerRowCount="1">
+  <autoFilter ref="A10:N41"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2459</v>
+        <v>2568</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1842</v>
+        <v>1921</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1145</v>
+        <v>1196</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="G11" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>265</v>
+      </c>
+      <c r="J11" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="H11" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>78</v>
-      </c>
       <c r="K11" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>23</v>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>5</v>
@@ -1103,16 +1103,16 @@
         <v>9</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>51</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>10</v>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>79</v>
@@ -1163,10 +1163,10 @@
         <v>22</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>5</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>17</v>
@@ -1211,16 +1211,16 @@
         <v>19</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>26</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>17</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>8</v>
@@ -1274,26 +1274,26 @@
         <v>44</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1307,47 +1307,47 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1361,35 +1361,35 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1415,19 +1415,19 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>23</v>
@@ -1436,7 +1436,7 @@
         <v>16</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>24</v>
@@ -1469,35 +1469,35 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>60</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1523,31 +1523,31 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>11</v>
@@ -1598,7 +1598,7 @@
         <v>14</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>4</v>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,35 +1685,35 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1742,13 +1742,13 @@
         <v>42</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>32</v>
@@ -1760,10 +1760,10 @@
         <v>12</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="G29" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H29" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="K29" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,20 +1843,20 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>25</v>
@@ -1865,13 +1865,13 @@
         <v>8</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
         <v>40</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="G31" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J31" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H31" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="K31" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>01086</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>RECCO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1955,31 +1955,31 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G32" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K32" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="L32" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="M32" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="M32" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01086</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>RECCO</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2009,31 +2009,31 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="G33" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="H33" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I33" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>113</v>
-      </c>
       <c r="M33" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2066,10 +2066,10 @@
         <v>26</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>33</v>
@@ -2084,10 +2084,10 @@
         <v>0</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2117,19 +2117,19 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>12</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>2</v>
@@ -2138,7 +2138,7 @@
         <v>1</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>2</v>
@@ -2171,28 +2171,28 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>20</v>
@@ -2234,7 +2234,7 @@
         <v>17</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>1</v>
@@ -2307,45 +2307,45 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01339</t>
+          <t>01409</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ALASSIO</t>
+          <t>NOVI LIGURE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>0</v>
@@ -2368,52 +2368,106 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>01339</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>ALASSIO</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>BARNABA SALVATORE</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>01416</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>SERRAVALLE SCRIVIA</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="E41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -2376,11 +2376,7 @@
           <t>ALASSIO</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>BARNABA SALVATORE</t>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N41" headerRowCount="1">
-  <autoFilter ref="A10:N41"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O41" headerRowCount="1">
+  <autoFilter ref="A10:O41"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>VIA G BRUNO 71</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>VIGNADUZZO EDI</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>345</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>465</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>265</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIA CANTORE 20 A ROSSO</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>371</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>330</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>475</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>256</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>288</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>CORSO ALESSANDRIA 494</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>VIGNADUZZO EDI</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>259</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>328</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>245</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>204</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>213</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>STALINGRADO</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>BARNABA SALVATORE</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>168</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>VIA BRIGATE PARTIGIANE, 1/R</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>249</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>129</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>426</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>VIA FERRIERE BRUZZO 13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>151</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>LUNGOBISAGNO D'ISTRIA</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>276</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>VIA RIGHETTI 1 R</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>154</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>CORSO GENOVA 40</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="F19" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>194</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>VIA NIZZA 152</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>VIA VITTORIO VENETO 52</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>VIA NAZIONALE PIEMONTE 68 R</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>STR PROV PER VALENZA 4/B</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>VIGNADUZZO EDI</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>STR. STATALE 31 KM 22+335</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>VIGNADUZZO EDI</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>S.S. 10</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>VIGNADUZZO EDI</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>CSO LIMONE PIEMONTE 1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>BARNABA SALVATORE</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>VIA GRAMSCI 9/A</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>VIA MAZZINI</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>BARNABA SALVATORE</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>VIA BRUNO PRIMI, 14</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>SS 28 KM 136 + 600</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>BARNABA SALVATORE</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>VIA SIFFREDI, 62</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>VIA ROMA</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>LOCALITA' MONTECAVALLO - VIA AURELIA 67/A</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="M33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>REGIONE PIEVE N.47</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>VIGNADUZZO EDI</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="I34" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>VIALE ITALIA 160</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="I35" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>CORSO DE STEFANIS 215/R</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="H36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="12" t="n">
         <v>19</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L36" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>VIA CISA 50</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="I37" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="J37" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="M37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="N37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2270,42 +2421,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>VIA AURELIA 256</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="K38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2324,20 +2480,22 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>VIA MAZZINI 56</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G39" s="12" t="n">
         <v>0</v>
       </c>
@@ -2345,11 +2503,11 @@
         <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
@@ -2359,7 +2517,10 @@
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="N39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2376,27 +2537,29 @@
           <t>ALASSIO</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>SAN GIOVANNI BOSCO</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>BARNABA SALVATORE</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J40" s="12" t="n">
         <v>0</v>
       </c>
@@ -2409,7 +2572,10 @@
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2428,29 +2594,31 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J41" s="12" t="n">
         <v>0</v>
       </c>
@@ -2458,12 +2626,15 @@
         <v>0</v>
       </c>
       <c r="L41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="N41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2568</v>
+        <v>2728</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1921</v>
+        <v>2023</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1196</v>
+        <v>1283</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>475</v>
+        <v>502</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>59</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>51</v>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>01351</t>
+          <t>01032</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>STALINGRADO</t>
+          <t>VIA BRIGATE PARTIGIANE, 1/R</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,56 +1015,56 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>168</v>
+        <v>453</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>01032</t>
+          <t>01351</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA BRIGATE PARTIGIANE, 1/R</t>
+          <t>STALINGRADO</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,39 +1074,39 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>249</v>
+        <v>157</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>426</v>
+        <v>174</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,35 +1137,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>51</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>5</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>26</v>
@@ -1276,31 +1276,31 @@
         <v>33</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA NIZZA 152</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>VIA NIZZA 152</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>11</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>16</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,35 +1609,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>20</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>11</v>
@@ -1689,10 +1689,10 @@
         <v>14</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>6</v>
@@ -1807,7 +1807,7 @@
         <v>18</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>3</v>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI</t>
+          <t>SS 28 KM 136 + 600</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1845,52 +1845,52 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA BRUNO PRIMI, 14</t>
+          <t>VIA MAZZINI</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>SS 28 KM 136 + 600</t>
+          <t>VIA BRUNO PRIMI, 14</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,35 +1959,35 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J30" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M30" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="N30" s="12" t="n">
         <v>25</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="M30" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="N30" s="12" t="n">
-        <v>26</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>40</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>9</v>
@@ -2043,14 +2043,14 @@
         <v>12</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>9</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>25</v>
@@ -2093,16 +2093,16 @@
         <v>19</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>3</v>
@@ -2140,19 +2140,19 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>5</v>
@@ -2161,7 +2161,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>46</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>8</v>
@@ -2220,10 +2220,10 @@
         <v>0</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIALE ITALIA 160</t>
+          <t>CORSO DE STEFANIS 215/R</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="H35" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="I35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J35" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="K35" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CORSO DE STEFANIS 215/R</t>
+          <t>VIALE ITALIA 160</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,39 +2313,39 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>26</v>
@@ -2385,19 +2385,19 @@
         <v>17</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>2</v>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01409</t>
+          <t>01416</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>NOVI LIGURE</t>
+          <t>SERRAVALLE SCRIVIA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI 56</t>
+          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2494,74 +2494,78 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01339</t>
+          <t>01409</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ALASSIO</t>
+          <t>NOVI LIGURE</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI BOSCO</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr"/>
+          <t>VIA MAZZINI 56</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>0</v>
@@ -2584,40 +2588,36 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>01416</t>
+          <t>01339</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SERRAVALLE SCRIVIA</t>
+          <t>ALASSIO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+          <t>SAN GIOVANNI BOSCO</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>0</v>
@@ -2629,14 +2629,14 @@
         <v>0</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2728</v>
+        <v>2868</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2023</v>
+        <v>2136</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1283</v>
+        <v>1357</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>497</v>
+        <v>524</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>520</v>
+        <v>547</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
+        <v>279</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>354</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>210</v>
+      </c>
+      <c r="I13" s="12" t="n">
         <v>268</v>
       </c>
-      <c r="G13" s="12" t="n">
-        <v>341</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>199</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>257</v>
-      </c>
       <c r="J13" s="12" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>59</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>51</v>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>68</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>453</v>
+        <v>475</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>5</v>
@@ -1149,19 +1149,19 @@
         <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>21</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,25 +1196,25 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>154</v>
@@ -1255,35 +1255,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I18" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="N18" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J18" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>165</v>
-      </c>
-      <c r="N18" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>9</v>
@@ -1326,16 +1326,16 @@
         <v>15</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA NIZZA 152</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>204</v>
+        <v>96</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA NIZZA 152</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,39 +1428,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>89</v>
+        <v>213</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>25</v>
@@ -1550,35 +1550,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="G23" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="G23" s="12" t="n">
-        <v>66</v>
-      </c>
       <c r="H23" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>31</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>10</v>
@@ -1630,10 +1630,10 @@
         <v>9</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>63</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA GRAMSCI 9/A</t>
+          <t>SS 28 KM 136 + 600</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SS 28 KM 136 + 600</t>
+          <t>VIA GRAMSCI 9/A</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I28" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K28" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI</t>
+          <t>VIA BRUNO PRIMI, 14</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>32</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA BRUNO PRIMI, 14</t>
+          <t>VIA MAZZINI</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,39 +1959,39 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>37</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>19</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>16</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>3</v>
@@ -2143,7 +2143,7 @@
         <v>34</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>15</v>
@@ -2161,7 +2161,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
@@ -2202,13 +2202,13 @@
         <v>27</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>28</v>
@@ -2220,10 +2220,10 @@
         <v>0</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>CORSO DE STEFANIS 215/R</t>
+          <t>VIALE ITALIA 160</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIALE ITALIA 160</t>
+          <t>CORSO DE STEFANIS 215/R</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,39 +2313,39 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M36" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="N36" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="J36" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="N36" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>26</v>
@@ -2394,10 +2394,10 @@
         <v>4</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
@@ -2456,31 +2456,31 @@
         <v>0</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01416</t>
+          <t>01409</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SERRAVALLE SCRIVIA</t>
+          <t>NOVI LIGURE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
+          <t>VIA MAZZINI 56</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2494,52 +2494,52 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01409</t>
+          <t>01416</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>NOVI LIGURE</t>
+          <t>SERRAVALLE SCRIVIA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI 56</t>
+          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2553,35 +2553,35 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2868</v>
+        <v>3023</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2136</v>
+        <v>2243</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1357</v>
+        <v>1430</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>524</v>
+        <v>560</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>547</v>
+        <v>577</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>532</v>
+        <v>560</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
+        <v>284</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>369</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>211</v>
+      </c>
+      <c r="I13" s="12" t="n">
         <v>279</v>
       </c>
-      <c r="G13" s="12" t="n">
-        <v>354</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>268</v>
-      </c>
       <c r="J13" s="12" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>51</v>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>5</v>
@@ -1149,19 +1149,19 @@
         <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>28</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>20</v>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,39 +1310,39 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="H19" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="K19" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="L19" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>6</v>
@@ -1385,19 +1385,19 @@
         <v>3</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>29</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,39 +1428,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>213</v>
+        <v>86</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>12</v>
@@ -1509,13 +1509,13 @@
         <v>26</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,35 +1550,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G23" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="H23" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>68</v>
-      </c>
       <c r="K23" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SS 28 KM 136 + 600</t>
+          <t>VIA GRAMSCI 9/A</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA GRAMSCI 9/A</t>
+          <t>SS 28 KM 136 + 600</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,39 +1841,39 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>8</v>
@@ -1984,10 +1984,10 @@
         <v>13</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>01086</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>RECCO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA SIFFREDI, 62</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01086</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>RECCO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA</t>
+          <t>VIA SIFFREDI, 62</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,39 +2077,39 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2140,19 +2140,19 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>5</v>
@@ -2161,7 +2161,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
@@ -2199,22 +2199,22 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>0</v>
@@ -2258,19 +2258,19 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>2</v>
@@ -2279,10 +2279,10 @@
         <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>3</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2376,35 +2376,35 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>28</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01409</t>
+          <t>01416</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>NOVI LIGURE</t>
+          <t>SERRAVALLE SCRIVIA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI 56</t>
+          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2494,52 +2494,52 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N39" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01416</t>
+          <t>01409</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SERRAVALLE SCRIVIA</t>
+          <t>NOVI LIGURE</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
+          <t>VIA MAZZINI 56</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2556,32 +2556,32 @@
         <v>3</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3023</v>
+        <v>3115</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2243</v>
+        <v>2319</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1430</v>
+        <v>1479</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>81</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         <v>284</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>211</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>227</v>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>69</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>28</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>5</v>
@@ -1149,7 +1149,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>23</v>
@@ -1158,10 +1158,10 @@
         <v>55</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,52 +1255,52 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>40</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA NIZZA 152</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="K19" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L19" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M19" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="N19" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L19" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>228</v>
-      </c>
-      <c r="N19" s="12" t="n">
-        <v>56</v>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA NIZZA 152</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>101</v>
+        <v>236</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,76 +1408,76 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>STR PROV PER VALENZA 4/B</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE PIEMONTE 68 R</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>127</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="M22" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="G22" s="12" t="n">
-        <v>155</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>126</v>
-      </c>
       <c r="N22" s="12" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,59 +1526,59 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>STR PROV PER VALENZA 4/B</t>
+          <t>VIA NAZIONALE PIEMONTE 68 R</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>7</v>
@@ -1745,10 +1745,10 @@
         <v>13</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>20</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>9</v>
@@ -1798,7 +1798,7 @@
         <v>18</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>10</v>
@@ -1807,10 +1807,10 @@
         <v>20</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2025,7 @@
         <v>43</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>30</v>
@@ -2043,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>3</v>
@@ -2084,7 +2084,7 @@
         <v>42</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>11</v>
@@ -2102,14 +2102,14 @@
         <v>12</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2140,19 +2140,19 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>5</v>
@@ -2161,7 +2161,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,31 +2258,31 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>3</v>
@@ -2338,10 +2338,10 @@
         <v>4</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2379,13 +2379,13 @@
         <v>20</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>17</v>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2497,13 +2497,13 @@
         <v>5</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>4</v>
@@ -2515,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3115</v>
+        <v>3252</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2319</v>
+        <v>2432</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1479</v>
+        <v>1546</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>588</v>
+        <v>620</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>605</v>
+        <v>643</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>585</v>
+        <v>622</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         <v>284</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>211</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>227</v>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>64</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>534</v>
+        <v>557</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>44</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1199,13 +1199,13 @@
         <v>149</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>92</v>
@@ -1217,14 +1217,14 @@
         <v>57</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>40</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA NIZZA 152</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1314,52 +1314,52 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA NIZZA 152</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,94 +1369,94 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="K20" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="N20" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L20" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>236</v>
-      </c>
-      <c r="N20" s="12" t="n">
-        <v>56</v>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>STR PROV PER VALENZA 4/B</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>92</v>
+        <v>250</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,59 +1467,59 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>STR PROV PER VALENZA 4/B</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>9</v>
@@ -1562,7 +1562,7 @@
         <v>12</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>27</v>
@@ -1571,7 +1571,7 @@
         <v>23</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>26</v>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>13</v>
@@ -1630,10 +1630,10 @@
         <v>9</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1789,13 +1789,13 @@
         <v>62</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>42</v>
@@ -1807,10 +1807,10 @@
         <v>20</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SS 28 KM 136 + 600</t>
+          <t>VIA BRUNO PRIMI, 14</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA BRUNO PRIMI, 14</t>
+          <t>SS 28 KM 136 + 600</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>8</v>
@@ -2043,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>3</v>
@@ -2081,19 +2081,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>14</v>
@@ -2140,19 +2140,19 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>5</v>
@@ -2161,7 +2161,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
@@ -2175,55 +2175,55 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>REGIONE PIEVE N.47</t>
+          <t>VIALE ITALIA 160</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,55 +2234,55 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIALE ITALIA 160</t>
+          <t>REGIONE PIEVE N.47</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>0</v>
@@ -2338,14 +2338,14 @@
         <v>4</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
         <v>19</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>17</v>
@@ -2494,19 +2494,19 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>2</v>
@@ -2515,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3252</v>
+        <v>3372</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2432</v>
+        <v>2521</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1546</v>
+        <v>1604</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>643</v>
+        <v>677</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>38</v>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>488</v>
+        <v>516</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>622</v>
+        <v>658</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         <v>284</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>211</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>227</v>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>557</v>
+        <v>597</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>8</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,76 +1290,76 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>STR PROV PER VALENZA 4/B</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA NIZZA 152</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>116</v>
+        <v>260</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,98 +1428,98 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>55</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>STR PROV PER VALENZA 4/B</t>
+          <t>VIA NIZZA 152</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>12</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>26</v>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>14</v>
@@ -1689,10 +1689,10 @@
         <v>20</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>50</v>
@@ -1745,13 +1745,13 @@
         <v>13</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>20</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>3</v>
@@ -2081,19 +2081,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>14</v>
@@ -2102,31 +2102,31 @@
         <v>12</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>LOCALITA' MONTECAVALLO - VIA AURELIA 67/A</t>
+          <t>VIALE ITALIA 160</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2140,31 +2140,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIALE ITALIA 160</t>
+          <t>LOCALITA' MONTECAVALLO - VIA AURELIA 67/A</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2199,16 +2199,16 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>36</v>
@@ -2217,13 +2217,13 @@
         <v>5</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,31 +2258,31 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>56</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2338,14 +2338,14 @@
         <v>4</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2379,13 +2379,13 @@
         <v>20</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>17</v>
@@ -2397,7 +2397,7 @@
         <v>4</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
@@ -2411,22 +2411,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>01416</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>VADO LIGURE</t>
+          <t>SERRAVALLE SCRIVIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA 256</t>
+          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2435,57 +2435,57 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G38" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="I38" s="12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K38" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01416</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SERRAVALLE SCRIVIA</t>
+          <t>VADO LIGURE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
+          <t>VIA AURELIA 256</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2494,35 +2494,35 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>71</v>
-      </c>
       <c r="J39" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="N39" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3372</v>
+        <v>3503</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2521</v>
+        <v>2628</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1604</v>
+        <v>1679</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>472</v>
+        <v>508</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>641</v>
+        <v>670</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>677</v>
+        <v>719</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>658</v>
+        <v>689</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>408</v>
+        <v>437</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         <v>284</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>211</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>227</v>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>60</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>41</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,52 +1314,52 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>260</v>
+        <v>108</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,39 +1428,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>101</v>
+        <v>271</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
         <v>102</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>6</v>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>12</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>13</v>
@@ -1630,10 +1630,10 @@
         <v>10</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1730,13 +1730,13 @@
         <v>75</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>50</v>
@@ -1748,10 +1748,10 @@
         <v>23</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>10</v>
@@ -1866,10 +1866,10 @@
         <v>18</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>22</v>
@@ -1916,19 +1916,19 @@
         <v>8</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,28 +1963,28 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>70</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>60</v>
@@ -2025,13 +2025,13 @@
         <v>47</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>32</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>30</v>
@@ -2043,10 +2043,10 @@
         <v>17</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>12</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>10</v>
@@ -2140,35 +2140,35 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>27</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>20</v>
@@ -2217,13 +2217,13 @@
         <v>5</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>56</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>45</v>
@@ -2279,14 +2279,14 @@
         <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>29</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>0</v>
@@ -2338,7 +2338,7 @@
         <v>4</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>27</v>
@@ -2385,7 +2385,7 @@
         <v>19</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>17</v>
@@ -2397,7 +2397,7 @@
         <v>4</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
@@ -2435,19 +2435,19 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>3</v>
@@ -2456,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>2</v>
@@ -2574,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>5</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -528,7 +528,7 @@
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">

--- a/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARRARO ANDREA.xlsx
@@ -684,13 +684,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3503</v>
+        <v>3508</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2628</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1679</v>
+        <v>1650</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>152</v>
@@ -863,10 +863,10 @@
         <v>110</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>123</v>
@@ -922,7 +922,7 @@
         <v>86</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>20</v>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>211</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>89</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>95</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>57</v>
@@ -1040,7 +1040,7 @@
         <v>71</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>39</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>50</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>68</v>
@@ -1099,7 +1099,7 @@
         <v>46</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>34</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>7</v>
@@ -1149,7 +1149,7 @@
         <v>14</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>28</v>
@@ -1158,7 +1158,7 @@
         <v>64</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>17</v>
@@ -1199,16 +1199,16 @@
         <v>156</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>29</v>
@@ -1217,7 +1217,7 @@
         <v>60</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>10</v>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>37</v>
@@ -1276,14 +1276,14 @@
         <v>41</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>102</v>
@@ -1323,10 +1323,10 @@
         <v>74</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>43</v>
@@ -1335,31 +1335,31 @@
         <v>15</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>76</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1373,52 +1373,52 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>108</v>
+        <v>267</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1435,32 +1435,32 @@
         <v>109</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="H21" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I21" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>271</v>
+        <v>107</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>6</v>
@@ -1503,7 +1503,7 @@
         <v>5</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>31</v>
@@ -1512,7 +1512,7 @@
         <v>25</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>12</v>
@@ -1553,7 +1553,7 @@
         <v>100</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>13</v>
@@ -1562,7 +1562,7 @@
         <v>12</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>31</v>
@@ -1571,7 +1571,7 @@
         <v>24</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>27</v>
@@ -1612,7 +1612,7 @@
         <v>90</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>26</v>
@@ -1621,7 +1621,7 @@
         <v>39</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>13</v>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>72</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>15</v>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>13</v>
@@ -1748,7 +1748,7 @@
         <v>23</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>24</v>
@@ -1789,7 +1789,7 @@
         <v>67</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>11</v>
@@ -1798,7 +1798,7 @@
         <v>22</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>11</v>
@@ -1807,31 +1807,31 @@
         <v>21</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>12</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA BRUNO PRIMI, 14</t>
+          <t>SS 28 KM 136 + 600</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>SS 28 KM 136 + 600</t>
+          <t>VIA BRUNO PRIMI, 14</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G29" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M29" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="H29" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>117</v>
-      </c>
       <c r="N29" s="12" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>12</v>
@@ -1984,10 +1984,10 @@
         <v>15</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2025,16 +2025,16 @@
         <v>47</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>8</v>
@@ -2043,7 +2043,7 @@
         <v>17</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>4</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA SIFFREDI, 62</t>
+          <t>VIALE ITALIA 160</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIALE ITALIA 160</t>
+          <t>VIA SIFFREDI, 62</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,35 +2136,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>20</v>
@@ -2211,7 +2211,7 @@
         <v>3</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>5</v>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>42</v>
@@ -2270,7 +2270,7 @@
         <v>45</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>12</v>
@@ -2279,14 +2279,14 @@
         <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>3</v>
@@ -2338,14 +2338,14 @@
         <v>4</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>27</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>4</v>
@@ -2397,7 +2397,7 @@
         <v>4</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
@@ -2447,7 +2447,7 @@
         <v>75</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>3</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>1</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
